--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,465 +656,478 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E8" s="3">
         <v>196300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>150500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>100200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>88800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>73600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>33300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>49100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>33300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>73900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>47400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>978200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3008800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>201800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2184600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>187300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>153800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>56100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>71300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>103300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>37700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>40300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>69800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>126000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>153300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E9" s="3">
         <v>181700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>133900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>90900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>95100</v>
       </c>
       <c r="H9" s="3">
         <v>95100</v>
       </c>
       <c r="I9" s="3">
+        <v>95100</v>
+      </c>
+      <c r="J9" s="3">
         <v>91000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>103100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>103100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>102400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>143900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>102800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>939900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>744000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1264100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>78300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>696800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>81900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>92900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>175000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>80700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>36000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>38600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>62700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>174600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E10" s="3">
         <v>14600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-6400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-21500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-19100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-54100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-69100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-54100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-69100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-70100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-47500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-892500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>234200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1744700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>123500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1487800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>105400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>60800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>27000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-103700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>112800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1151,112 +1164,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E12" s="3">
         <v>11500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>16600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>118100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>205100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>117900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>5500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1359,67 +1376,70 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E14" s="3">
         <v>8800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>33900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>65500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>65500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="3">
         <v>67200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>30400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>16</v>
+      <c r="U14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>16</v>
@@ -1427,8 +1447,8 @@
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1463,50 +1483,53 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E15" s="3">
         <v>11900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>17600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8200</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1519,8 +1542,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>16</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>16</v>
@@ -1540,15 +1563,15 @@
       <c r="AA15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AB15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC15" s="3">
         <v>500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>400</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1558,8 +1581,8 @@
       <c r="AG15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH15" s="3">
-        <v>0</v>
+      <c r="AH15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AI15" s="3">
         <v>0</v>
@@ -1567,8 +1590,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1602,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E17" s="3">
         <v>211100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>173200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>128100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>140800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>124800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>123600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>136000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>140500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>136000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>140500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>183800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>140900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>183600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1030300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1816100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>116300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>971300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>121400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>130200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>58000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>37700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>29000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>21800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>194700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>79600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>16100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>51200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>79700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>188800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-22700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-27900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-52000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-51200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-51800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-86900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-107200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-86900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-107200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-110000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-85700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-136200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-52100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1192700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>85500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1213300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>65900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-123400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>102400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1848,154 +1881,158 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E20" s="3">
         <v>59800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-70200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>9900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>9900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>110200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>147200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>123400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>9800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-80600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-62800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-33300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-42500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-81900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-86500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-81900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-86500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-89600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-78900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2032,40 +2069,43 @@
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="3">
         <v>16500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-39400</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AJ21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
-      </c>
-      <c r="E22" s="3">
-        <v>400</v>
       </c>
       <c r="F22" s="3">
         <v>400</v>
@@ -2074,13 +2114,13 @@
         <v>300</v>
       </c>
       <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>16</v>
@@ -2097,23 +2137,23 @@
       <c r="O22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2125,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>200</v>
@@ -2137,192 +2177,198 @@
         <v>200</v>
       </c>
       <c r="AC22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD22" s="3">
         <v>300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2700</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>2400</v>
       </c>
       <c r="AH22" s="3">
         <v>2400</v>
       </c>
       <c r="AI22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-84200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-82300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-43800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-162100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-162100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-116100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-86700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-123500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1339800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>86000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1336600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>72800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-122900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>106600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>85300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-23100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-20400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-23100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-20400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>304400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>20900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>49800</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -2354,22 +2400,25 @@
         <v>0</v>
       </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-8100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2472,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-85000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-27700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-92900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-75600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-139000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-80100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-139000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-80100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-84400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>61100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1035500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>65100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1286900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>72800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-122900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>14600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>93300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-85000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-27700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-92900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-75600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-139000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-80100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-139000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-80100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-110700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-84400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>61100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1035500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>65100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1286900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>72800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-122900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>14600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>93300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2784,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2888,8 +2949,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2992,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3096,216 +3163,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-59800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>70200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-9900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-9900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-110200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-147200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-123400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-85000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-27700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-92900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-75600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-139000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-80100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-139000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-80100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-110700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-84400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>61100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1035500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>65100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1286900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>72800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>23900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-122900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>14600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>93300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3408,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-85000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-27700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-92900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-75600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-139000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-80100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-139000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-80100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-110700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-84400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>61100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1035500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>65100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1286900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>72800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>23900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-122900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>14600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>93300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3659,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3697,95 +3783,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E41" s="3">
         <v>80800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>119200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>65900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>96500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>66800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>96200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>96200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>40600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>66100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>72000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>101600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2002700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2640700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2643200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2684300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>241400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>173500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>186200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>54500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>41400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>80400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>51200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>42200</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3801,41 +3888,44 @@
       <c r="AJ41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
         <v>2100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>3300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>3700</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3864,32 +3954,32 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>1200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>30100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>51200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>27100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>12500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>17200</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3905,95 +3995,98 @@
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E43" s="3">
         <v>129800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>114700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>59700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q43" s="3">
         <v>504300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>357900</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>275000</v>
-      </c>
-      <c r="U43" s="3">
-        <v>100</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
       </c>
       <c r="W43" s="3">
+        <v>100</v>
+      </c>
+      <c r="X43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>14000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>24800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>26400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>16</v>
       </c>
@@ -4009,95 +4102,98 @@
       <c r="AJ43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>128800</v>
+      </c>
+      <c r="E44" s="3">
         <v>180800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>201700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>108000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>87800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>131300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>142300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>217100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>142300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>217100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>272100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>310500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1685600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1328900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1626200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1193300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>812400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>118400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>83500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>52400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>31400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>13000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>35500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>30200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>60400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>65500</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>16</v>
       </c>
@@ -4113,95 +4209,98 @@
       <c r="AJ44" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E45" s="3">
         <v>39700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3">
         <v>117300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3">
         <v>74900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>63100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="3">
         <v>63100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1427300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1335300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1420300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1937600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1501800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>186200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>201800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>82800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>31700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>37000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>26600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>74700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>64800</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4217,95 +4316,98 @@
       <c r="AJ45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>310600</v>
+      </c>
+      <c r="E46" s="3">
         <v>433300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>517400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>421000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>334000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>307500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>336000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>363700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>349200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>363700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>349200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>431800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>520800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>555700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5024700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5687200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5774100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5273500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>546200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>458800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>323500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>140200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>101100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>115400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>145900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>144900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>222500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>216100</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4321,13 +4423,16 @@
       <c r="AJ46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2800</v>
+        <v>12800</v>
       </c>
       <c r="E47" s="3">
         <v>2800</v>
@@ -4339,10 +4444,10 @@
         <v>2800</v>
       </c>
       <c r="H47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I47" s="3">
         <v>2900</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2800</v>
       </c>
       <c r="J47" s="3">
         <v>2800</v>
@@ -4360,13 +4465,13 @@
         <v>2800</v>
       </c>
       <c r="O47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="P47" s="3">
         <v>2900</v>
       </c>
       <c r="Q47" s="3">
-        <v>20000</v>
+        <v>2900</v>
       </c>
       <c r="R47" s="3">
         <v>20000</v>
@@ -4378,11 +4483,11 @@
         <v>20000</v>
       </c>
       <c r="U47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="V47" s="3">
         <v>2800</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
@@ -4390,11 +4495,11 @@
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
         <v>400</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4410,8 +4515,8 @@
       <c r="AE47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
+      <c r="AF47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AG47" s="3">
         <v>0</v>
@@ -4425,95 +4530,98 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E48" s="3">
         <v>46900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>63700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>72700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>46000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>53400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>717200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>355400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>357200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>340600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>216500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>21200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8200</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4529,31 +4637,34 @@
       <c r="AJ48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E49" s="3">
         <v>700</v>
       </c>
       <c r="F49" s="3">
+        <v>700</v>
+      </c>
+      <c r="G49" s="3">
         <v>800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1000</v>
       </c>
       <c r="I49" s="3">
         <v>1000</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4571,34 +4682,34 @@
         <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>12500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>74100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>51300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>45300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>900</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -4633,8 +4744,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4737,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4841,70 +4958,73 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>92600</v>
+      </c>
+      <c r="E52" s="3">
         <v>119000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>85100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>94600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>81400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>71200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>70300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>107300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>70600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>102000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>500</v>
-      </c>
-      <c r="W52" s="3">
-        <v>400</v>
       </c>
       <c r="X52" s="3">
         <v>400</v>
@@ -4913,23 +5033,23 @@
         <v>400</v>
       </c>
       <c r="Z52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA52" s="3">
         <v>300</v>
       </c>
       <c r="AB52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC52" s="3">
         <v>800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1000</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4945,8 +5065,11 @@
       <c r="AJ52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5049,95 +5172,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>446200</v>
+      </c>
+      <c r="E54" s="3">
         <v>602900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>670000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>592200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>463000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>502100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>525500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>493300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>464100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>493300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>464100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>538400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>633700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>685000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5581400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6194700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6250500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5632300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>558400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>465900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>328700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>144300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>106800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>133900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>152500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>152700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>245800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>225300</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5153,8 +5279,11 @@
       <c r="AJ54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5191,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5229,95 +5359,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E57" s="3">
         <v>25600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>32700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>97000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>101200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>143400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>17100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>15300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5333,50 +5464,53 @@
       <c r="AJ57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E58" s="3">
         <v>30200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>46400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>17900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5396,32 +5530,32 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>4500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>28900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>29700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>19600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>38300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>30800</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5437,95 +5571,98 @@
       <c r="AJ58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E59" s="3">
         <v>42300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>143400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>160000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>123400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>96900</v>
       </c>
-      <c r="I59" s="3">
-        <v>65200</v>
-      </c>
       <c r="J59" s="3">
+        <v>66900</v>
+      </c>
+      <c r="K59" s="3">
         <v>101000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>99600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>395300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>658600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1379100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2093600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1941700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>188600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>176100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>236300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>70500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>53200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>54400</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5541,95 +5678,98 @@
       <c r="AJ59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E60" s="3">
         <v>131100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>279000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>236900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>178600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>151200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>116800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>135200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>135200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>83000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>691300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1476100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2194800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2085100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>205700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>191400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>247100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>82500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>24500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>36300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>45700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>43900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>103000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>94900</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5645,50 +5785,53 @@
       <c r="AJ60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E61" s="3">
         <v>24700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5749,95 +5892,98 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9700</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3">
         <v>9400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>85100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>88500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2900</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5853,8 +5999,11 @@
       <c r="AJ62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5957,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6061,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6165,95 +6320,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>153500</v>
+      </c>
+      <c r="E66" s="3">
         <v>165500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>290100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>268600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>196800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>186300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>147300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>145100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>145100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>85600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>77300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>710000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1492900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2280000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2173600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>208300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>201900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>248300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>84100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>26700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>49000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>46000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>105700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>97800</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6269,8 +6427,11 @@
       <c r="AJ66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6307,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6411,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6515,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6619,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6723,95 +6894,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-832200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-645900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-560800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-533100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-435600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-342700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-267100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-204700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-65700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-204700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-65700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>14400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>125100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>209400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1932800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1886700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1277800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>900800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-65800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-121100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-152700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-152900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-151300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-138500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-144500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-136000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6827,8 +7001,11 @@
       <c r="AJ72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6931,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7035,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7139,95 +7322,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E76" s="3">
         <v>437400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>379900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>323600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>266300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>315800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>378200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>348200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>363400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>348200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>363400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>426100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>548100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>607700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4871400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4701800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3970600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3458700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>350100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>264000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>80500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>80100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>95000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>103500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>106700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>140100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>127500</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7243,8 +7429,11 @@
       <c r="AJ76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7347,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-97600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-85000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-27700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-92900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-75600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-139000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-80100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-139000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-80100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-110700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-84400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-96300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>61100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1035500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>65100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1286900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>72800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>23900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-122900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>14600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>93300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7598,8 +7796,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7621,26 +7820,26 @@
       <c r="I83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="3">
         <v>14900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M83" s="3">
         <v>14900</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -7681,8 +7880,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>16</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>16</v>
@@ -7702,8 +7901,11 @@
       <c r="AJ83" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7806,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7910,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8014,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8118,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8222,8 +8436,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8263,15 +8480,15 @@
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-182600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-582200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
@@ -8284,8 +8501,8 @@
       <c r="V89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -8305,8 +8522,8 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>16</v>
+      <c r="AD89" s="3">
+        <v>0</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>16</v>
@@ -8326,8 +8543,11 @@
       <c r="AJ89" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8364,8 +8584,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8405,8 +8626,8 @@
       <c r="O91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -8447,8 +8668,8 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>16</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>16</v>
@@ -8468,8 +8689,11 @@
       <c r="AJ91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8572,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8676,8 +8903,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8717,15 +8947,15 @@
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-40300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8738,8 +8968,8 @@
       <c r="V94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -8759,8 +8989,8 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>16</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>16</v>
@@ -8780,8 +9010,11 @@
       <c r="AJ94" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8818,8 +9051,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8859,8 +9093,8 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8922,8 +9156,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9026,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9130,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9234,8 +9477,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9275,15 +9521,15 @@
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-56200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-315600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
@@ -9296,8 +9542,8 @@
       <c r="V100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -9317,8 +9563,8 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>16</v>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>16</v>
@@ -9338,8 +9584,11 @@
       <c r="AJ100" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9361,33 +9610,33 @@
       <c r="I101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3">
         <v>-110300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M101" s="3">
         <v>-110300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-80000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>209000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
@@ -9400,8 +9649,8 @@
       <c r="V101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -9421,8 +9670,8 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>16</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>16</v>
@@ -9442,8 +9691,11 @@
       <c r="AJ101" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9484,14 +9736,14 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-326900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-729000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
@@ -9504,8 +9756,8 @@
       <c r="V102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
@@ -9525,8 +9777,8 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>16</v>
+      <c r="AD102" s="3">
+        <v>0</v>
       </c>
       <c r="AE102" s="3" t="s">
         <v>16</v>
@@ -9544,6 +9796,9 @@
         <v>16</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
